--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>122302098</v>
       </c>
       <c r="B3" t="n">
-        <v>105280</v>
+        <v>105290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122298081</v>
+        <v>122302098</v>
       </c>
       <c r="B2" t="n">
-        <v>57527</v>
+        <v>105303</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falkviken, Nedre Glottern, Ög</t>
+          <t>Falkviken OSO 785 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571306</v>
+        <v>571289</v>
       </c>
       <c r="R2" t="n">
-        <v>6506477</v>
+        <v>6506472</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +764,9 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,28 +775,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302098</v>
+        <v>122298081</v>
       </c>
       <c r="B3" t="n">
-        <v>105290</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,57 +811,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkviken OSO 785 m, Ög</t>
+          <t>Falkviken, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571289</v>
+        <v>571306</v>
       </c>
       <c r="R3" t="n">
-        <v>6506472</v>
+        <v>6506477</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,9 +884,19 @@
           <t>2025-01-24</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,24 +905,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122302098</v>
       </c>
       <c r="B2" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302098</v>
+        <v>122298081</v>
       </c>
       <c r="B2" t="n">
-        <v>105308</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,57 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falkviken OSO 785 m, Ög</t>
+          <t>Falkviken, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571289</v>
+        <v>571306</v>
       </c>
       <c r="R2" t="n">
-        <v>6506472</v>
+        <v>6506477</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,9 +755,19 @@
           <t>2025-01-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,34 +776,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122298081</v>
+        <v>122302098</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>105317</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,53 +806,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkviken, Nedre Glottern, Ög</t>
+          <t>Falkviken OSO 785 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571306</v>
+        <v>571289</v>
       </c>
       <c r="R3" t="n">
-        <v>6506477</v>
+        <v>6506472</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,19 +878,9 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,18 +889,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122298081</v>
+        <v>122302098</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>105330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221144</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falkviken, Nedre Glottern, Ög</t>
+          <t>Falkviken OSO 785 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571306</v>
+        <v>571289</v>
       </c>
       <c r="R2" t="n">
-        <v>6506477</v>
+        <v>6506472</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +764,9 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,28 +775,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302098</v>
+        <v>122298081</v>
       </c>
       <c r="B3" t="n">
-        <v>105317</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,52 +811,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkviken OSO 785 m, Ög</t>
+          <t>Falkviken, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571289</v>
+        <v>571306</v>
       </c>
       <c r="R3" t="n">
-        <v>6506472</v>
+        <v>6506477</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,9 +884,19 @@
           <t>2025-01-24</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,24 +905,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302098</v>
+        <v>122298081</v>
       </c>
       <c r="B2" t="n">
-        <v>105330</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,57 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falkviken OSO 785 m, Ög</t>
+          <t>Falkviken, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571289</v>
+        <v>571306</v>
       </c>
       <c r="R2" t="n">
-        <v>6506472</v>
+        <v>6506477</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,9 +760,19 @@
           <t>2025-01-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,34 +781,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122298081</v>
+        <v>122302098</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>105343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,53 +811,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkviken, Nedre Glottern, Ög</t>
+          <t>Falkviken OSO 785 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571306</v>
+        <v>571289</v>
       </c>
       <c r="R3" t="n">
-        <v>6506477</v>
+        <v>6506472</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,19 +888,9 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,18 +899,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122298081</v>
+        <v>122302098</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>105343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falkviken, Nedre Glottern, Ög</t>
+          <t>Falkviken OSO 785 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571306</v>
+        <v>571289</v>
       </c>
       <c r="R2" t="n">
-        <v>6506477</v>
+        <v>6506472</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +764,9 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,28 +775,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302098</v>
+        <v>122298081</v>
       </c>
       <c r="B3" t="n">
-        <v>105343</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,57 +811,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkviken OSO 785 m, Ög</t>
+          <t>Falkviken, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571289</v>
+        <v>571306</v>
       </c>
       <c r="R3" t="n">
-        <v>6506472</v>
+        <v>6506477</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,9 +884,19 @@
           <t>2025-01-24</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,24 +905,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302098</v>
+        <v>122298081</v>
       </c>
       <c r="B2" t="n">
-        <v>105343</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,57 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falkviken OSO 785 m, Ög</t>
+          <t>Falkviken, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571289</v>
+        <v>571306</v>
       </c>
       <c r="R2" t="n">
-        <v>6506472</v>
+        <v>6506477</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,9 +760,19 @@
           <t>2025-01-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,34 +781,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122298081</v>
+        <v>122302098</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>105346</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,53 +811,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkviken, Nedre Glottern, Ög</t>
+          <t>Falkviken OSO 785 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571306</v>
+        <v>571289</v>
       </c>
       <c r="R3" t="n">
-        <v>6506477</v>
+        <v>6506472</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,19 +888,9 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,18 +899,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122298081</v>
+        <v>122302098</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>105347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,57 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falkviken, Nedre Glottern, Ög</t>
+          <t>Falkviken OSO 785 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571306</v>
+        <v>571289</v>
       </c>
       <c r="R2" t="n">
-        <v>6506477</v>
+        <v>6506472</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +764,9 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,28 +775,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122302098</v>
+        <v>122298081</v>
       </c>
       <c r="B3" t="n">
-        <v>105346</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,57 +811,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkviken OSO 785 m, Ög</t>
+          <t>Falkviken, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571289</v>
+        <v>571306</v>
       </c>
       <c r="R3" t="n">
-        <v>6506472</v>
+        <v>6506477</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,9 +884,19 @@
           <t>2025-01-24</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,24 +905,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122302098</v>
       </c>
       <c r="B2" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 60900-2024 artfynd.xlsx
+++ b/artfynd/A 60900-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122302098</v>
+        <v>122298081</v>
       </c>
       <c r="B2" t="n">
-        <v>105350</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,57 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falkviken OSO 785 m, Ög</t>
+          <t>Falkviken, Nedre Glottern, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571289</v>
+        <v>571306</v>
       </c>
       <c r="R2" t="n">
-        <v>6506472</v>
+        <v>6506477</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,9 +760,19 @@
           <t>2025-01-24</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-01-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,34 +781,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Petter  Jonsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122298081</v>
+        <v>122302098</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>105350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,53 +811,57 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Falkviken, Nedre Glottern, Ög</t>
+          <t>Falkviken OSO 785 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571306</v>
+        <v>571289</v>
       </c>
       <c r="R3" t="n">
-        <v>6506477</v>
+        <v>6506472</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,19 +888,9 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,18 +899,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petter  Jonsson</t>
+          <t>Mirjam Ideström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
